--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q117"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -577,6 +587,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -652,6 +672,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -727,6 +757,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -802,6 +842,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -877,6 +927,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -952,6 +1012,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1027,6 +1097,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1102,6 +1182,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1177,6 +1267,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1252,6 +1352,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1327,6 +1437,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1402,6 +1522,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1477,6 +1607,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1552,6 +1692,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1627,6 +1777,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1702,6 +1862,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1777,6 +1947,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1852,6 +2032,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1927,6 +2117,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2002,6 +2202,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2077,6 +2287,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2152,6 +2372,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2227,6 +2457,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2302,6 +2542,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2377,6 +2627,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2452,6 +2712,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2527,6 +2797,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2602,6 +2882,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2677,6 +2967,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2752,6 +3052,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2827,6 +3137,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2902,6 +3222,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2977,6 +3307,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3052,6 +3392,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3127,6 +3477,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3202,6 +3562,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3277,6 +3647,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3352,6 +3732,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3427,6 +3817,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3502,6 +3902,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3577,6 +3987,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3652,6 +4072,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3727,6 +4157,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3802,6 +4242,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3877,6 +4327,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3952,6 +4412,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4027,6 +4497,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4102,6 +4582,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4177,6 +4667,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4252,6 +4752,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4327,6 +4837,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4402,6 +4922,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4477,6 +5007,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4552,6 +5092,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4627,6 +5177,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4702,6 +5262,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4777,6 +5347,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4852,6 +5432,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4927,6 +5517,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5002,6 +5602,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5077,6 +5687,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5152,6 +5772,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5227,6 +5857,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5302,6 +5942,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5377,6 +6027,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5452,6 +6112,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5527,6 +6197,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5602,6 +6282,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5677,6 +6367,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5752,6 +6452,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5827,6 +6537,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5902,6 +6622,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5977,6 +6707,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6052,6 +6792,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6127,6 +6877,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6202,6 +6962,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6277,6 +7047,16 @@
           <t>150201</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6352,6 +7132,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6427,6 +7217,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6502,6 +7302,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6577,6 +7387,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6652,6 +7472,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6727,6 +7557,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6802,6 +7642,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6877,6 +7727,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6952,6 +7812,16 @@
           <t>150205</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7027,6 +7897,16 @@
           <t>150205</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7102,6 +7982,16 @@
           <t>150205</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7177,6 +8067,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7252,6 +8152,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7327,6 +8237,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7402,6 +8322,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7477,6 +8407,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7552,6 +8492,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7627,6 +8577,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7702,6 +8662,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7777,6 +8747,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7852,6 +8832,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7927,6 +8917,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8002,6 +9002,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8077,6 +9087,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8152,6 +9172,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8227,6 +9257,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8302,6 +9342,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8377,6 +9427,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8452,6 +9512,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8527,6 +9597,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8600,6 +9680,16 @@
       <c r="Q109" t="inlineStr">
         <is>
           <t>150110</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
         </is>
       </c>
     </row>
@@ -8657,6 +9747,8 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8712,6 +9804,8 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8787,6 +9881,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8862,6 +9966,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8937,6 +10051,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9012,6 +10136,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9087,6 +10221,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9160,6 +10304,16 @@
       <c r="Q117" t="inlineStr">
         <is>
           <t>150143</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S117"/>
+  <dimension ref="A1:T117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -597,6 +602,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -682,6 +692,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -767,6 +782,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -852,6 +872,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -937,6 +962,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1022,6 +1052,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1107,6 +1142,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1192,6 +1232,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1277,6 +1322,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1362,6 +1412,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1447,6 +1502,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1532,6 +1592,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1617,6 +1682,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1702,6 +1772,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1787,6 +1862,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1872,6 +1952,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1957,6 +2042,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2042,6 +2132,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2127,6 +2222,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2212,6 +2312,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2297,6 +2402,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2382,6 +2492,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2467,6 +2582,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2552,6 +2672,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2637,6 +2762,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2722,6 +2852,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2807,6 +2942,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2892,6 +3032,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2977,6 +3122,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3062,6 +3212,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3147,6 +3302,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3232,6 +3392,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3317,6 +3482,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3402,6 +3572,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3487,6 +3662,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3572,6 +3752,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3657,6 +3842,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3742,6 +3932,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3827,6 +4022,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3912,6 +4112,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3997,6 +4202,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4082,6 +4292,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4167,6 +4382,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4252,6 +4472,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4337,6 +4562,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4422,6 +4652,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4507,6 +4742,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4592,6 +4832,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4677,6 +4922,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4762,6 +5012,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4847,6 +5102,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4932,6 +5192,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5017,6 +5282,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5102,6 +5372,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5187,6 +5462,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5272,6 +5552,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5357,6 +5642,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5442,6 +5732,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5527,6 +5822,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5612,6 +5912,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5697,6 +6002,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5782,6 +6092,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5867,6 +6182,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5952,6 +6272,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6037,6 +6362,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6122,6 +6452,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6207,6 +6542,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6292,6 +6632,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6377,6 +6722,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6462,6 +6812,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6547,6 +6902,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6632,6 +6992,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6717,6 +7082,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6802,6 +7172,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6887,6 +7262,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6972,6 +7352,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7057,6 +7442,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7142,6 +7532,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7227,6 +7622,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7312,6 +7712,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7397,6 +7802,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7482,6 +7892,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7567,6 +7982,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7652,6 +8072,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7737,6 +8162,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7822,6 +8252,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7907,6 +8342,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7992,6 +8432,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8077,6 +8522,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8162,6 +8612,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8247,6 +8702,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8332,6 +8792,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8417,6 +8882,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8502,6 +8972,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8587,6 +9062,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8672,6 +9152,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8757,6 +9242,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8842,6 +9332,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8927,6 +9422,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9012,6 +9512,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9097,6 +9602,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9182,6 +9692,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9267,6 +9782,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9352,6 +9872,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9437,6 +9962,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9522,6 +10052,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9607,6 +10142,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9692,6 +10232,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9742,13 +10287,42 @@
         <v>1</v>
       </c>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9799,13 +10373,42 @@
         <v>1</v>
       </c>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9891,6 +10494,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9976,6 +10584,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10061,6 +10674,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10146,6 +10764,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10231,6 +10854,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10314,6 +10942,11 @@
       <c r="S117" t="inlineStr">
         <is>
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>UGME</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T117"/>
+  <dimension ref="A1:V117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -604,6 +614,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>3057/3057/3057 SANTA ROSA DE CARABAYLLO</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -694,6 +714,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>3057/3057/3057 SANTA ROSA DE CARABAYLLO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -784,6 +814,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -874,6 +914,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -964,6 +1014,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1054,6 +1114,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1144,6 +1214,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1234,6 +1314,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1324,6 +1414,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1414,6 +1514,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>SAN MARTIN DE PORRES/2077 SAN MARTIN DE PORRES DE AÑO NUEVO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1504,6 +1614,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>8156 PERUANO ALEMAN</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1594,6 +1714,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>PERU-HOLANDA/PERU-HOLANDA</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1684,6 +1814,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>PERU-HOLANDA/PERU-HOLANDA</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1774,6 +1914,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>2026 SIMON BOLIVAR/2026 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1864,6 +2014,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>2026 SIMON BOLIVAR/2026 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1954,6 +2114,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>8170 CESAR VALLEJO/8170 CESAR VALLEJO/8170 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2044,6 +2214,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>8170 CESAR VALLEJO/8170 CESAR VALLEJO/8170 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2134,6 +2314,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2224,6 +2414,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2314,6 +2514,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2404,6 +2614,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2494,6 +2714,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2584,6 +2814,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2674,6 +2914,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2764,6 +3014,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2854,6 +3114,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2944,6 +3214,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>SANTA LUZMILA</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3034,6 +3314,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>2016 CHAVIN DE HUANTAR</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3124,6 +3414,16 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3214,6 +3514,16 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
+          <t>2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO/2022 PEDRO ABRAHAM VALDELOMAR PINTO</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3304,6 +3614,16 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>2025 INMACULADA CONCEPCION/2025 INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3394,6 +3714,16 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>2025 INMACULADA CONCEPCION/2025 INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3484,6 +3814,16 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>3087/3087</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3574,6 +3914,16 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>PALMAS REALES</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3664,6 +4014,16 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>ALFREDO REBAZA ACOSTA</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3754,6 +4114,16 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
+          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3844,6 +4214,16 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3934,6 +4314,16 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
+          <t>0026 SAN ROQUE</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4024,6 +4414,16 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
+          <t>110 SAN MARCOS/110 SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4114,6 +4514,16 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
+          <t>115-17 SAN JUDAS TADEO</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4204,6 +4614,16 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
+          <t>115-17 SAN JUDAS TADEO</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4294,6 +4714,16 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
+          <t>107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4384,6 +4814,16 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4474,6 +4914,16 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA/107 DANIEL ALCIDES CARRION GARCIA</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4564,6 +5014,16 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
+          <t>MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4654,6 +5114,16 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
+          <t>MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4744,6 +5214,16 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
+          <t>MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE/MANUEL CASALINO GRIEVE</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4834,6 +5314,16 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
+          <t>652 03 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4924,6 +5414,16 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
+          <t>7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5014,6 +5514,16 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
+          <t>7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5104,6 +5614,16 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
+          <t>7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5194,6 +5714,16 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
+          <t>7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES/7072 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5284,6 +5814,16 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
+          <t>7215 NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5374,6 +5914,16 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
+          <t>7216/7216</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5464,6 +6014,16 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
+          <t>7236 MAX UHLE/7236 MAX UHLE</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5554,6 +6114,16 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
+          <t>7236 MAX UHLE/7236 MAX UHLE</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5644,6 +6214,16 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5734,6 +6314,16 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
+          <t>641 INCA PACHACUTEC</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5824,6 +6414,16 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
+          <t>6084 SAN MARTIN DE PORRES/652 30/6084 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5914,6 +6514,16 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
+          <t>6014/6014</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6004,6 +6614,16 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
+          <t>7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6094,6 +6714,16 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
+          <t>7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6184,6 +6814,16 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
+          <t>7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA/7057 SOBERANA ORDEN MILITAR DE MALTA</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6274,6 +6914,16 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
+          <t>7088 VICE-ALMIRANTE GERONIMO CAFFERATA MARAZZI/7088 VICE-ALMIRANTE GERONIMO CAFFERATA MARAZZI</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6364,6 +7014,16 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
+          <t>7106 VILLA LIMATAMBO/7106 VILLA LIMATAMBO</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6454,6 +7114,16 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
+          <t>7106 VILLA LIMATAMBO/7106 VILLA LIMATAMBO</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6544,6 +7214,16 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6634,6 +7314,16 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6724,6 +7414,16 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6814,6 +7514,16 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6904,6 +7614,16 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6994,6 +7714,16 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7084,6 +7814,16 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
+          <t>JOSE GALVEZ BARRENECHEA</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7174,6 +7914,16 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7264,6 +8014,16 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7354,6 +8114,16 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
+          <t>7235 MARISCAL ANDRES AVELINO CACERES/7235 MARISCAL ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7444,6 +8214,16 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
+          <t>21571 RICARDO PALMA SORIANO/21571 RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7534,6 +8314,16 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
+          <t>PATIVILCA/PATIVILCA/20505 VIRGEN INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7624,6 +8414,16 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
+          <t>20506 JOSE A ENCINAS FRANCO/20506 JOSE A ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7714,6 +8514,16 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
+          <t>20506 JOSE A ENCINAS FRANCO/20506 JOSE A ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7804,6 +8614,16 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
+          <t>20504 SAN JERONIMO/20504 SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7894,6 +8714,16 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
+          <t>20504 SAN JERONIMO/20504 SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7984,6 +8814,16 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
+          <t>JOSE PARDO Y BARREDA</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8074,6 +8914,16 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
+          <t>JOSE PARDO Y BARREDA</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8164,6 +9014,16 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
+          <t>JOSE PARDO Y BARREDA</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8254,6 +9114,16 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
+          <t>PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8344,6 +9214,16 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
+          <t>PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8434,6 +9314,16 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
+          <t>PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8524,6 +9414,16 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
+          <t>MARISCAL CHAPERITO</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8614,6 +9514,16 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
+          <t>MARISCAL CHAPERITO</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8704,6 +9614,16 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
+          <t>6073 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8794,6 +9714,16 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
+          <t>6073 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8884,6 +9814,16 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
+          <t>6073 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8974,6 +9914,16 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
+          <t>7215 NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9064,6 +10014,16 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
+          <t>21004-3</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9154,6 +10114,16 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
+          <t>MI NUEVA CASITA</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9244,6 +10214,16 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
+          <t>MI NUEVA CASITA</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9334,6 +10314,16 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
+          <t>VILLA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9424,6 +10414,16 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
+          <t>VILLA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9514,6 +10514,16 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
+          <t>CARRUSEL I</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9604,6 +10614,16 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
+          <t>CARRUSEL I</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9694,6 +10714,16 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
+          <t>LAS ESTRELLITAS</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9784,6 +10814,16 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
+          <t>LAS ESTRELLITAS</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9874,6 +10914,16 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
+          <t>URBANIZACION PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9964,6 +11014,16 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
+          <t>PASITO A PASO</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10054,6 +11114,16 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
+          <t>NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10144,6 +11214,16 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
+          <t>MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10234,6 +11314,16 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
+          <t>SEÑOR DE LOS MILAGROS I</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10320,6 +11410,16 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
+          <t>MI NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10406,6 +11506,16 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
+          <t>MI NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10496,6 +11606,16 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
+          <t>LA ALBORADA</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10586,6 +11706,16 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
+          <t>LA ALBORADA</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10676,6 +11806,16 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
+          <t>RAYITOS DE ESPERANZA</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10766,6 +11906,16 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
+          <t>RAYITOS DE ESPERANZA</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10856,6 +12006,16 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
+          <t>MI MUNDO DE COLORES I</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10945,6 +12105,16 @@
         </is>
       </c>
       <c r="T117" t="inlineStr">
+        <is>
+          <t>MI MUNDO DE COLORES I</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
         <is>
           <t>UGME</t>
         </is>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
@@ -11392,7 +11392,11 @@
           <t>VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>150142</t>
@@ -11488,7 +11492,11 @@
           <t>VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>150142</t>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_conservacion.xlsx
@@ -419,62 +419,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código modular</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>LOCALES EDUCATIVOS</t>
+          <t>locales_educativos</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Grupo (Aula Domo, Aula Modular, Escuela Modular, Módulo SS.HH., Pararrayo, Redes Complementarias, etc.)</t>
+          <t>grupo_aula_domo_aula_modular_escuela_modular_modulo_ss_hh_pa</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Descripción del bien</t>
+          <t>descripcion_del_bien</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>AÑO DE INSTALACIÓN</t>
+          <t>ano_de_instalacion</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Fecha de inicio (o estimada)</t>
+          <t>fecha_inicio</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Estado (No iniciado, en proceso, culminado)</t>
+          <t>estado_no_iniciado_en_proceso_culminado</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Monto contractual (S/)</t>
+          <t>monto_contractual</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Total de bienes</t>
+          <t>total_de_bienes</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
